--- a/TESTS/zlit_7_oldridzh.xlsx
+++ b/TESTS/zlit_7_oldridzh.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Джеймс Олдрідж — австралійський письменник що жив у Британії і писав про пригоди і людську силу духу</t>
+          <t>Джеймс Олдрідж</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>У пустелі та морі поблизу Червоного моря — батько і маленький син опиняються сам на сам з небезпекою</t>
+          <t>У пустелі та морі поблизу Червоного моря</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Бен — льотчик бере сина Деві на зйомку акул і потрапляє у смертельну небезпеку після нападу акули</t>
+          <t>Бен</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Акула жорстоко покалічила йому руки і плечі — він тяжко поранений але мусить якось повернутись до літака</t>
+          <t>Акула жорстоко покалічила йому руки і плечі</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Незважаючи на важкі рани дістатись до літака і відлетіти — інакше обидва загинуть</t>
+          <t>Незважаючи на важкі рани дістатись до літака і відлетіти</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Маленький хлопчик веде літак під керівництвом батька — робить те чого ніколи раніше не вмів</t>
+          <t>Маленький хлопчик веде літак під керівництвом батька</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Дюйм — гранична малість; «останній дюйм» — той фінальний крок через себе що відокремлює виживання від загибелі</t>
+          <t>Дюйм</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>До — відчуженість і незрозуміння; після — небезпека зближує їх і відкриває справжні почуття</t>
+          <t>До</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -939,6 +984,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чому Бен — батько Деві — полетів до Акулячої бухти, попри те що вона вважалась небезпечним місцем?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він хотів пригод</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він знімав підводних акул для продажу фотографій — це була його робота</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він шукав скарби</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він рятував когось</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чому Деві взагалі опинився в цій поїздці разом з батьком?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він сам організував поїздку</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Батько неочікувано взяв його, бо дитину нікуди дівати — не з любові, а з вимушеності</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Деві просив взяти його давно</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Так сталось випадково</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Яким є стосунок між Беном і Деві на початку оповідання?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Теплим і близьким</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Холодним і відчуженим — батько не вміє говорити з сином і уникає близькості</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ворожим і конфліктним</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Байдужим, але коректним</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Що Деві робив на березі, поки батько пірнав?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Спав</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спостерігав за морем і літаком, відчуваючи себе зайвим і непотрібним</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Готував їжу</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ловив рибу</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Як акула вдарила Бена під час пірнання?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Знизу у ногу</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Раптово і жорстоко покалічила обидві руки і плечі — рани були дуже серйозні</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Злегка зачепила бік</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вкусила за ногу лише раз</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як Бен дістався берега після нападу акули?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його врятував дельфін</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кинув спорядження і останніми силами виплив на мілководдя, де Деві допоміг його витягнути</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він не міг рухатись і потонув</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Деві поплив за ним у море</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Чому Бен не міг сам пілотувати літак після нападу акули?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він злякався</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидві руки були жорстоко покалічені — він не міг тримати штурвал</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він непритомнів від жаху</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ноги відмовили</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як Бен давав Деві інструкції з пілотування?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Через рацію здалеку</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Голосом — крок за кроком, попри нестерпний біль і слабкість</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він написав записку</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він показував жестами</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що означав для Деві кожен наступний крок у пілотуванні?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Все було просто і легко</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він долав власний страх і невідомість, щоразу роблячи те, чого ніколи не робив</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він усе знав, бо бачив по телевізору</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не боявся зовсім</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Яку внутрішню боротьбу вів Деві під час посадки?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Боявся гарматного пострілу</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Паніка і невпевненість проти рішучості врятувати батька — він не мав права здатись</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сумнівався, чи варто рятувати батька</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Думав про маму</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що особливо важливо у тому, що саме Деві вів літак, а не дорослий?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Це нічого особливого</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дитина взяла на себе відповідальність дорослого рішення у критичній ситуації, де не було іншого виходу</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Діти зазвичай добре літають</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Батько сам захотів так</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Як Бен змінився в поводженні з Деві під час аварії, порівняно з поведінкою до неї?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він не змінився</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вперше в житті він відкрився синові і говорив з ним чесно — потреба виживання зняла стіну між ними</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він став ще суворішим</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він перестав говорити зовсім</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що символізує назва «Останній дюйм» у оповіданні?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Конкретну відстань при посадці</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ту гранично малу відстань між смертю і порятунком — фізичну і психологічну</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Висоту, на якій летів літак</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Різницю у росту між батьком і сином</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>У чому «останній дюйм» між батьком і сином у людському сенсі?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони жили далеко одне від одного</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дистанція у стосунках між ними — яку вони подолали у критичний момент, коли обоє відкрились один до одного</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони були різного зросту</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони не знали одне одного в обличчя</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Які слова Бен першим сказав Деві після посадки — і чому вони важливі?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>«Непогано, але міг краще»</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Слова подяки і визнання сина — перші справжні слова від холодного батька, що змінило їхні стосунки</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>«Я так і знав, що ти зможеш»</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>«Піди подзвони в лікарню»</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Як оповідання «Останній дюйм» схоже на «Жагу до життя» Джека Лондона?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Однакові герої</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва — про людину (або людей) на межі смерті, де виживання залежить від волі до боротьби</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Обидва про дітей-пілотів</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Обидва про море і акул</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Яку педагогічну цінність має «Останній дюйм» для підлітків?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Жодної спеціальної</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Показує, що відповідальність і відвага не залежать від віку — підліток здатен на більше, ніж йому здається</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вчить пілотувати літак</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вчить боятись акул</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чим реалістичний опис поранення і польоту важливий для сприйняття оповідання?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Реалізм не важливий</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Точні деталі роблять небезпеку справжньою — читач разом з Деві відчуває всю вагу кожного рішення</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він лише уповільнює темп</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Деталі потрібні для наукової точності</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Чи змінились стосунки батька і сина після пережитого?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ні, все залишилось як раніше</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Так — пережите разом відкрило їх один до одного, заклавши основу для справжньої близькості</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони ніколи більше не бачились</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони посварились більше, ніж раніше</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Що символізує образ акул у ширшому контексті оповідання?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Конкретну зоологічну небезпеку</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>І реальну смертельну небезпеку, і метафору безжального зовнішнього світу, що змушує людину відкритись</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Природу Червоного моря</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Необережність Бена</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яка головна ідея «Останнього дюйма»?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не літайте у небезпечні місця</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Найважчі ситуації можуть стати моментом, коли люди нарешті знаходять одне одного</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Акули небезпечні і слід їх уникати</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Батьки завжди знають краще за дітей</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє точний реалістичний опис у оповіданні?</t>
+          <t>Реалістичний точний опис рани і польоту у оповіданні робить небезпеку справжньою і змушує читача переживати разом з героями.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Чим «Останній дюйм» схожий на оповідання Джека Лондона «Жага до життя»?</t>
+          <t>«Останній дюйм» і «Жага до життя» об'єднує тема боротьби людини за виживання на межі фізичних можливостей.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку педагогічну цінність має «Останній дюйм» для підлітків?</t>
+          <t>Педагогічна цінність «Останнього дюйма» для підлітків нульова, бо це лише пригодницька розповідь без морального виміру.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея оповідання «Останній дюйм»?</t>
+          <t>Головна ідея «Останнього дюйма» — у найважчий момент людина може знайти в собі ресурс і одночасно знайти іншу людину поруч.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що тема батька і сина означає в оповіданні Олдріджа?</t>
+          <t>Тема батька і сина у оповіданні Олдріджа — це тема подолання відчуженості через спільне випробування.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Чому «Останній дюйм» є класикою літератури про виживання?</t>
+          <t>«Останній дюйм» є класикою літератури про виживання, бо точно показує психологію людини під тиском смертельної небезпеки.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми розкриває «Останній дюйм»?</t>
+          <t>Що відбувається в «Останньому дюймі»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Сила духу у критичній ситуації</t>
+          <t>Акула жорстоко поранила Бену руки і плечі</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Взаємопорозуміння між батьком і сином</t>
+          <t>Деві вів літак за інструкцією пораненого батька</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Небезпека акул</t>
+          <t>Бен спокійно пілотував сам до фінішу</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Відповідальність дитини в дорослій ситуації</t>
+          <t>Батько і син зближуються через спільне випробування</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Спільна боротьба за виживання — смертельна небезпека відкрила те що звичайне життя приховувало</t>
+          <t>Спільна боротьба за виживання</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Через страх і незнання але з величезною силою волі — він тягне «останній дюйм» щоб врятувати батька</t>
+          <t>Через страх і незнання але з величезною силою волі</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
